--- a/artfynd/A 27805-2022 artfynd.xlsx
+++ b/artfynd/A 27805-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -779,6 +779,234 @@
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>121452935</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57504</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Storvallen B, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>356522</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7019013</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-04-09</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-04-09</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Ulla Falkdalen</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Ulla Falkdalen</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>121453015</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57462</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Storvallen B, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>356522</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7019013</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-04-09</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-04-09</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Ulla Falkdalen</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Ulla Falkdalen</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27805-2022 artfynd.xlsx
+++ b/artfynd/A 27805-2022 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121452935</v>
+        <v>121453015</v>
       </c>
       <c r="B3" t="n">
-        <v>57504</v>
+        <v>57462</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,30 +793,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>103031</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121453015</v>
+        <v>121452935</v>
       </c>
       <c r="B4" t="n">
-        <v>57462</v>
+        <v>57504</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -907,30 +907,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103031</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>

--- a/artfynd/A 27805-2022 artfynd.xlsx
+++ b/artfynd/A 27805-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1007,6 +1007,112 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>121504481</v>
+      </c>
+      <c r="B5" t="n">
+        <v>78607</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Storvallen B, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>356522</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7019013</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-04-09</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-04-09</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Ulla Falkdalen</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Ulla Falkdalen</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27805-2022 artfynd.xlsx
+++ b/artfynd/A 27805-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121453015</v>
+        <v>121452935</v>
       </c>
       <c r="B3" t="n">
-        <v>57462</v>
+        <v>57507</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,30 +793,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103031</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121452935</v>
+        <v>121453015</v>
       </c>
       <c r="B4" t="n">
-        <v>57504</v>
+        <v>57465</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -907,30 +907,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>103031</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -1113,6 +1113,348 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>121512139</v>
+      </c>
+      <c r="B6" t="n">
+        <v>56785</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100091</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Storspov</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Numenius arquata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Lilltevedalen 1:27, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>357448</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7019833</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-06-09</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-06-09</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Ulla Falkdalen</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Ulla Falkdalen</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>121512256</v>
+      </c>
+      <c r="B7" t="n">
+        <v>56818</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>102961</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Drillsnäppa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Actitis hypoleucos</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Storvallen S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>356388</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7018822</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-06-09</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-06-09</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Ulla Falkdalen</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Ulla Falkdalen</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>121512168</v>
+      </c>
+      <c r="B8" t="n">
+        <v>56762</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>102952</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tofsvipa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Vanellus vanellus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Lilltevedalen 1:27, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>357448</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7019833</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-06-09</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-06-09</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Ulla Falkdalen</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Ulla Falkdalen</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27805-2022 artfynd.xlsx
+++ b/artfynd/A 27805-2022 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121452935</v>
+        <v>121453015</v>
       </c>
       <c r="B3" t="n">
-        <v>57507</v>
+        <v>57465</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,30 +793,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>103031</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121453015</v>
+        <v>121452935</v>
       </c>
       <c r="B4" t="n">
-        <v>57465</v>
+        <v>57507</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -907,30 +907,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103031</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -1115,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121512139</v>
+        <v>121512256</v>
       </c>
       <c r="B6" t="n">
-        <v>56785</v>
+        <v>56818</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1127,25 +1127,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100091</v>
+        <v>102961</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Storspov</t>
+          <t>Drillsnäppa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Numenius arquata</t>
+          <t>Actitis hypoleucos</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,14 +1163,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lilltevedalen 1:27, Jmt</t>
+          <t>Storvallen S, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>357448</v>
+        <v>356388</v>
       </c>
       <c r="R6" t="n">
-        <v>7019833</v>
+        <v>7018822</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1229,10 +1229,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121512256</v>
+        <v>121512139</v>
       </c>
       <c r="B7" t="n">
-        <v>56818</v>
+        <v>56785</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1241,25 +1241,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102961</v>
+        <v>100091</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Drillsnäppa</t>
+          <t>Storspov</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Actitis hypoleucos</t>
+          <t>Numenius arquata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1277,14 +1277,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Storvallen S, Jmt</t>
+          <t>Lilltevedalen 1:27, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>356388</v>
+        <v>357448</v>
       </c>
       <c r="R7" t="n">
-        <v>7018822</v>
+        <v>7019833</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>

--- a/artfynd/A 27805-2022 artfynd.xlsx
+++ b/artfynd/A 27805-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1455,6 +1455,462 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>121548517</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57466</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Storvallen F, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>356746</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7019244</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-04-09</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-04-09</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Ulla Falkdalen</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Ulla Falkdalen</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>121548518</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57508</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Storvallen F, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>356746</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7019244</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-04-09</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-04-09</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Ulla Falkdalen</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Ulla Falkdalen</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>121548824</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57355</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Storvallen F, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>356746</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7019244</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2021-04-15</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2021-04-15</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Ulla Falkdalen</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Ulla Falkdalen</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>121548543</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57999</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103042</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Grönfink</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Chloris chloris</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Storvallen F, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>356746</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7019244</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-04-09</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-04-09</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Ulla Falkdalen</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Ulla Falkdalen</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27805-2022 artfynd.xlsx
+++ b/artfynd/A 27805-2022 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>121453015</v>
       </c>
       <c r="B3" t="n">
-        <v>57465</v>
+        <v>57466</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>121452935</v>
       </c>
       <c r="B4" t="n">
-        <v>57507</v>
+        <v>57508</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>121504481</v>
       </c>
       <c r="B5" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>121512256</v>
       </c>
       <c r="B6" t="n">
-        <v>56818</v>
+        <v>56819</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>121512139</v>
       </c>
       <c r="B7" t="n">
-        <v>56785</v>
+        <v>56786</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>121512168</v>
       </c>
       <c r="B8" t="n">
-        <v>56762</v>
+        <v>56763</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1457,10 +1457,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121548517</v>
+        <v>121548543</v>
       </c>
       <c r="B9" t="n">
-        <v>57466</v>
+        <v>57999</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1469,20 +1469,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103031</v>
+        <v>103042</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1492,14 +1492,14 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1685,10 +1685,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121548824</v>
+        <v>121548517</v>
       </c>
       <c r="B11" t="n">
-        <v>57355</v>
+        <v>57466</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1697,20 +1697,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1720,14 +1720,14 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1767,12 +1767,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2021-04-15</t>
+          <t>2024-04-09</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2021-04-15</t>
+          <t>2024-04-09</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1799,10 +1799,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121548543</v>
+        <v>121548824</v>
       </c>
       <c r="B12" t="n">
-        <v>57999</v>
+        <v>57355</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1811,20 +1811,20 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103042</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1834,14 +1834,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1881,12 +1881,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-04-09</t>
+          <t>2021-04-15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-04-09</t>
+          <t>2021-04-15</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 27805-2022 artfynd.xlsx
+++ b/artfynd/A 27805-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1115,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121512256</v>
+        <v>121548543</v>
       </c>
       <c r="B6" t="n">
-        <v>56819</v>
+        <v>57999</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1127,25 +1127,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102961</v>
+        <v>103042</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Drillsnäppa</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Actitis hypoleucos</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,14 +1163,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Storvallen S, Jmt</t>
+          <t>Storvallen F, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>356388</v>
+        <v>356746</v>
       </c>
       <c r="R6" t="n">
-        <v>7018822</v>
+        <v>7019244</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1197,12 +1197,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-04-09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-04-09</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1229,10 +1229,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121512139</v>
+        <v>121548518</v>
       </c>
       <c r="B7" t="n">
-        <v>56786</v>
+        <v>57508</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1241,50 +1241,50 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100091</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Storspov</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Numenius arquata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lilltevedalen 1:27, Jmt</t>
+          <t>Storvallen F, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>357448</v>
+        <v>356746</v>
       </c>
       <c r="R7" t="n">
-        <v>7019833</v>
+        <v>7019244</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1311,12 +1311,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-04-09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-04-09</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1343,10 +1343,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121512168</v>
+        <v>121548517</v>
       </c>
       <c r="B8" t="n">
-        <v>56763</v>
+        <v>57466</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1355,20 +1355,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102952</v>
+        <v>103031</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tofsvipa</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Vanellus vanellus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1385,20 +1385,20 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lilltevedalen 1:27, Jmt</t>
+          <t>Storvallen F, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>357448</v>
+        <v>356746</v>
       </c>
       <c r="R8" t="n">
-        <v>7019833</v>
+        <v>7019244</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1425,12 +1425,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-04-09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-04-09</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1457,10 +1457,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121548543</v>
+        <v>121548824</v>
       </c>
       <c r="B9" t="n">
-        <v>57999</v>
+        <v>57355</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1469,20 +1469,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103042</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1492,14 +1492,14 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-04-09</t>
+          <t>2021-04-15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-04-09</t>
+          <t>2021-04-15</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1568,348 +1568,6 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>121548518</v>
-      </c>
-      <c r="B10" t="n">
-        <v>57508</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Storvallen F, Jmt</t>
-        </is>
-      </c>
-      <c r="Q10" t="n">
-        <v>356746</v>
-      </c>
-      <c r="R10" t="n">
-        <v>7019244</v>
-      </c>
-      <c r="S10" t="n">
-        <v>25</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>2024-04-09</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>2024-04-09</t>
-        </is>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>Ulla Falkdalen</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>Ulla Falkdalen</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>121548517</v>
-      </c>
-      <c r="B11" t="n">
-        <v>57466</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>103031</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Lavskrika</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Perisoreus infaustus</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Storvallen F, Jmt</t>
-        </is>
-      </c>
-      <c r="Q11" t="n">
-        <v>356746</v>
-      </c>
-      <c r="R11" t="n">
-        <v>7019244</v>
-      </c>
-      <c r="S11" t="n">
-        <v>25</v>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>2024-04-09</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>2024-04-09</t>
-        </is>
-      </c>
-      <c r="AD11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT11" t="inlineStr"/>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>Ulla Falkdalen</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>Ulla Falkdalen</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>121548824</v>
-      </c>
-      <c r="B12" t="n">
-        <v>57355</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Storvallen F, Jmt</t>
-        </is>
-      </c>
-      <c r="Q12" t="n">
-        <v>356746</v>
-      </c>
-      <c r="R12" t="n">
-        <v>7019244</v>
-      </c>
-      <c r="S12" t="n">
-        <v>25</v>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>2021-04-15</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>2021-04-15</t>
-        </is>
-      </c>
-      <c r="AD12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="inlineStr"/>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>Ulla Falkdalen</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>Ulla Falkdalen</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 27805-2022 artfynd.xlsx
+++ b/artfynd/A 27805-2022 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>121453015</v>
       </c>
       <c r="B3" t="n">
-        <v>57466</v>
+        <v>57467</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>121452935</v>
       </c>
       <c r="B4" t="n">
-        <v>57508</v>
+        <v>57509</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>121504481</v>
       </c>
       <c r="B5" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1115,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121548543</v>
+        <v>121548518</v>
       </c>
       <c r="B6" t="n">
-        <v>57999</v>
+        <v>57509</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1127,37 +1127,37 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103042</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1229,10 +1229,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121548518</v>
+        <v>121548821</v>
       </c>
       <c r="B7" t="n">
-        <v>57508</v>
+        <v>57467</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1241,25 +1241,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>103031</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1311,12 +1311,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-04-09</t>
+          <t>2021-04-15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-04-09</t>
+          <t>2021-04-15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1343,10 +1343,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121548517</v>
+        <v>121548543</v>
       </c>
       <c r="B8" t="n">
-        <v>57466</v>
+        <v>58000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1355,20 +1355,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103031</v>
+        <v>103042</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1378,14 +1378,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1460,7 +1460,7 @@
         <v>121548824</v>
       </c>
       <c r="B9" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 27805-2022 artfynd.xlsx
+++ b/artfynd/A 27805-2022 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121453015</v>
+        <v>121452935</v>
       </c>
       <c r="B3" t="n">
-        <v>57467</v>
+        <v>57509</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,30 +793,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103031</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121452935</v>
+        <v>121453015</v>
       </c>
       <c r="B4" t="n">
-        <v>57509</v>
+        <v>57467</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -907,30 +907,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>103031</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>

--- a/artfynd/A 27805-2022 artfynd.xlsx
+++ b/artfynd/A 27805-2022 artfynd.xlsx
@@ -1229,10 +1229,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121548821</v>
+        <v>121548543</v>
       </c>
       <c r="B7" t="n">
-        <v>57467</v>
+        <v>58000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1241,20 +1241,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103031</v>
+        <v>103042</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1264,14 +1264,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1311,12 +1311,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2021-04-15</t>
+          <t>2024-04-09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2021-04-15</t>
+          <t>2024-04-09</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1343,10 +1343,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121548543</v>
+        <v>121548821</v>
       </c>
       <c r="B8" t="n">
-        <v>58000</v>
+        <v>57467</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1355,20 +1355,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103042</v>
+        <v>103031</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1378,14 +1378,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1425,12 +1425,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-04-09</t>
+          <t>2021-04-15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-04-09</t>
+          <t>2021-04-15</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 27805-2022 artfynd.xlsx
+++ b/artfynd/A 27805-2022 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121452935</v>
+        <v>121453015</v>
       </c>
       <c r="B3" t="n">
-        <v>57509</v>
+        <v>57467</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,30 +793,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>103031</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121453015</v>
+        <v>121452935</v>
       </c>
       <c r="B4" t="n">
-        <v>57467</v>
+        <v>57509</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -907,30 +907,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103031</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -1115,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121548518</v>
+        <v>121548517</v>
       </c>
       <c r="B6" t="n">
-        <v>57509</v>
+        <v>57467</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1127,25 +1127,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>103031</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1229,10 +1229,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121548543</v>
+        <v>121548518</v>
       </c>
       <c r="B7" t="n">
-        <v>58000</v>
+        <v>57509</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1241,37 +1241,37 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103042</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1343,10 +1343,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121548821</v>
+        <v>121548543</v>
       </c>
       <c r="B8" t="n">
-        <v>57467</v>
+        <v>58000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1355,20 +1355,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103031</v>
+        <v>103042</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1378,14 +1378,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1425,12 +1425,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2021-04-15</t>
+          <t>2024-04-09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2021-04-15</t>
+          <t>2024-04-09</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 27805-2022 artfynd.xlsx
+++ b/artfynd/A 27805-2022 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>121453015</v>
       </c>
       <c r="B3" t="n">
-        <v>57467</v>
+        <v>57468</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>121452935</v>
       </c>
       <c r="B4" t="n">
-        <v>57509</v>
+        <v>57510</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>121504481</v>
       </c>
       <c r="B5" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>121548517</v>
       </c>
       <c r="B6" t="n">
-        <v>57467</v>
+        <v>57468</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>121548518</v>
       </c>
       <c r="B7" t="n">
-        <v>57509</v>
+        <v>57510</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>121548543</v>
       </c>
       <c r="B8" t="n">
-        <v>58000</v>
+        <v>58001</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>121548824</v>
       </c>
       <c r="B9" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 27805-2022 artfynd.xlsx
+++ b/artfynd/A 27805-2022 artfynd.xlsx
@@ -1115,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121548821</v>
+        <v>121548518</v>
       </c>
       <c r="B6" t="n">
-        <v>57468</v>
+        <v>57510</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1127,25 +1127,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103031</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-04-15</t>
+          <t>2024-04-09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-04-15</t>
+          <t>2024-04-09</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1343,10 +1343,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121548518</v>
+        <v>121548517</v>
       </c>
       <c r="B8" t="n">
-        <v>57510</v>
+        <v>57468</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1355,25 +1355,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>103031</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">

--- a/artfynd/A 27805-2022 artfynd.xlsx
+++ b/artfynd/A 27805-2022 artfynd.xlsx
@@ -1115,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121548518</v>
+        <v>121548821</v>
       </c>
       <c r="B6" t="n">
-        <v>57510</v>
+        <v>57468</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1127,25 +1127,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>103031</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-04-09</t>
+          <t>2021-04-15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-04-09</t>
+          <t>2021-04-15</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1229,10 +1229,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121548543</v>
+        <v>121548518</v>
       </c>
       <c r="B7" t="n">
-        <v>58001</v>
+        <v>57510</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1241,37 +1241,37 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103042</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1343,10 +1343,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121548517</v>
+        <v>121548543</v>
       </c>
       <c r="B8" t="n">
-        <v>57468</v>
+        <v>58001</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1355,20 +1355,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103031</v>
+        <v>103042</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1378,14 +1378,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>

--- a/artfynd/A 27805-2022 artfynd.xlsx
+++ b/artfynd/A 27805-2022 artfynd.xlsx
@@ -1115,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121548821</v>
+        <v>121548543</v>
       </c>
       <c r="B6" t="n">
-        <v>57468</v>
+        <v>58001</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1127,20 +1127,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103031</v>
+        <v>103042</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1150,14 +1150,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1197,12 +1197,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-04-15</t>
+          <t>2024-04-09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-04-15</t>
+          <t>2024-04-09</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1229,10 +1229,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121548518</v>
+        <v>121548821</v>
       </c>
       <c r="B7" t="n">
-        <v>57510</v>
+        <v>57468</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1241,25 +1241,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>103031</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1311,12 +1311,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-04-09</t>
+          <t>2021-04-15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-04-09</t>
+          <t>2021-04-15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1343,10 +1343,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121548543</v>
+        <v>121548518</v>
       </c>
       <c r="B8" t="n">
-        <v>58001</v>
+        <v>57510</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1355,37 +1355,37 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103042</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>

--- a/artfynd/A 27805-2022 artfynd.xlsx
+++ b/artfynd/A 27805-2022 artfynd.xlsx
@@ -1115,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121548543</v>
+        <v>121548821</v>
       </c>
       <c r="B6" t="n">
-        <v>58001</v>
+        <v>57468</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1127,20 +1127,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103042</v>
+        <v>103031</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1150,14 +1150,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1197,12 +1197,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-04-09</t>
+          <t>2021-04-15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-04-09</t>
+          <t>2021-04-15</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1229,10 +1229,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121548821</v>
+        <v>121548518</v>
       </c>
       <c r="B7" t="n">
-        <v>57468</v>
+        <v>57510</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1241,25 +1241,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103031</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1311,12 +1311,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2021-04-15</t>
+          <t>2024-04-09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2021-04-15</t>
+          <t>2024-04-09</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1343,10 +1343,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121548518</v>
+        <v>121548543</v>
       </c>
       <c r="B8" t="n">
-        <v>57510</v>
+        <v>58001</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1355,37 +1355,37 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>103042</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>

--- a/artfynd/A 27805-2022 artfynd.xlsx
+++ b/artfynd/A 27805-2022 artfynd.xlsx
@@ -1115,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121548821</v>
+        <v>121548543</v>
       </c>
       <c r="B6" t="n">
-        <v>57468</v>
+        <v>58001</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1127,20 +1127,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103031</v>
+        <v>103042</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1150,14 +1150,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1197,12 +1197,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-04-15</t>
+          <t>2024-04-09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-04-15</t>
+          <t>2024-04-09</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1229,10 +1229,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121548518</v>
+        <v>121548517</v>
       </c>
       <c r="B7" t="n">
-        <v>57510</v>
+        <v>57468</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1241,25 +1241,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>103031</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1343,10 +1343,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121548543</v>
+        <v>121548518</v>
       </c>
       <c r="B8" t="n">
-        <v>58001</v>
+        <v>57510</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1355,37 +1355,37 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103042</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>

--- a/artfynd/A 27805-2022 artfynd.xlsx
+++ b/artfynd/A 27805-2022 artfynd.xlsx
@@ -1115,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121548543</v>
+        <v>121548518</v>
       </c>
       <c r="B6" t="n">
-        <v>58001</v>
+        <v>57510</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1127,37 +1127,37 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103042</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1229,7 +1229,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121548517</v>
+        <v>121548821</v>
       </c>
       <c r="B7" t="n">
         <v>57468</v>
@@ -1311,12 +1311,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-04-09</t>
+          <t>2021-04-15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-04-09</t>
+          <t>2021-04-15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1343,10 +1343,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121548518</v>
+        <v>121548543</v>
       </c>
       <c r="B8" t="n">
-        <v>57510</v>
+        <v>58001</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1355,37 +1355,37 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>103042</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>

--- a/artfynd/A 27805-2022 artfynd.xlsx
+++ b/artfynd/A 27805-2022 artfynd.xlsx
@@ -1460,7 +1460,7 @@
         <v>121548824</v>
       </c>
       <c r="B9" t="n">
-        <v>57357</v>
+        <v>57365</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 27805-2022 artfynd.xlsx
+++ b/artfynd/A 27805-2022 artfynd.xlsx
@@ -1574,7 +1574,7 @@
         <v>127032210</v>
       </c>
       <c r="B10" t="n">
-        <v>41361</v>
+        <v>41365</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 27805-2022 artfynd.xlsx
+++ b/artfynd/A 27805-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1574,7 +1574,7 @@
         <v>127032210</v>
       </c>
       <c r="B10" t="n">
-        <v>41365</v>
+        <v>41367</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1693,6 +1693,125 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>127742491</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57823</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Storvallen skog, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>356872</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7019203</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Ulla Falkdalen</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Ulla Falkdalen</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 27805-2022 artfynd.xlsx
+++ b/artfynd/A 27805-2022 artfynd.xlsx
@@ -1699,7 +1699,7 @@
         <v>127742491</v>
       </c>
       <c r="B11" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 27805-2022 artfynd.xlsx
+++ b/artfynd/A 27805-2022 artfynd.xlsx
@@ -1699,7 +1699,7 @@
         <v>127742491</v>
       </c>
       <c r="B11" t="n">
-        <v>57826</v>
+        <v>57832</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 27805-2022 artfynd.xlsx
+++ b/artfynd/A 27805-2022 artfynd.xlsx
@@ -1699,7 +1699,7 @@
         <v>127742491</v>
       </c>
       <c r="B11" t="n">
-        <v>57832</v>
+        <v>57833</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 27805-2022 artfynd.xlsx
+++ b/artfynd/A 27805-2022 artfynd.xlsx
@@ -1699,7 +1699,7 @@
         <v>127742491</v>
       </c>
       <c r="B11" t="n">
-        <v>57833</v>
+        <v>57845</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 27805-2022 artfynd.xlsx
+++ b/artfynd/A 27805-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1813,6 +1813,216 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128669862</v>
+      </c>
+      <c r="B12" t="n">
+        <v>98483</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220093</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Åre (väg 1018) - Storlien - Norska gränsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>356859</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7019308</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Noemi Naszarkowski, Anne van Woerkom</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>C250065 AVK krokom och sveg</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128669913</v>
+      </c>
+      <c r="B13" t="n">
+        <v>97520</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>222112</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Månlåsbräken</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Botrychium lunaria</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Sw.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Åre (väg 1018) - Storlien - Norska gränsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>357033</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7019072</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Noemi Naszarkowski, Anne van Woerkom</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>C250065 AVK krokom och sveg</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27805-2022 artfynd.xlsx
+++ b/artfynd/A 27805-2022 artfynd.xlsx
@@ -1818,7 +1818,7 @@
         <v>128669862</v>
       </c>
       <c r="B12" t="n">
-        <v>98483</v>
+        <v>98489</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         <v>128669913</v>
       </c>
       <c r="B13" t="n">
-        <v>97520</v>
+        <v>97526</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 27805-2022 artfynd.xlsx
+++ b/artfynd/A 27805-2022 artfynd.xlsx
@@ -1818,7 +1818,7 @@
         <v>128669862</v>
       </c>
       <c r="B12" t="n">
-        <v>98489</v>
+        <v>98492</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         <v>128669913</v>
       </c>
       <c r="B13" t="n">
-        <v>97526</v>
+        <v>97528</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 27805-2022 artfynd.xlsx
+++ b/artfynd/A 27805-2022 artfynd.xlsx
@@ -1818,7 +1818,7 @@
         <v>128669862</v>
       </c>
       <c r="B12" t="n">
-        <v>98492</v>
+        <v>98495</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 27805-2022 artfynd.xlsx
+++ b/artfynd/A 27805-2022 artfynd.xlsx
@@ -1818,7 +1818,7 @@
         <v>128669862</v>
       </c>
       <c r="B12" t="n">
-        <v>98495</v>
+        <v>98496</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         <v>128669913</v>
       </c>
       <c r="B13" t="n">
-        <v>97528</v>
+        <v>97529</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 27805-2022 artfynd.xlsx
+++ b/artfynd/A 27805-2022 artfynd.xlsx
@@ -1818,7 +1818,7 @@
         <v>128669862</v>
       </c>
       <c r="B12" t="n">
-        <v>98496</v>
+        <v>98523</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         <v>128669913</v>
       </c>
       <c r="B13" t="n">
-        <v>97529</v>
+        <v>97556</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 27805-2022 artfynd.xlsx
+++ b/artfynd/A 27805-2022 artfynd.xlsx
@@ -1818,7 +1818,7 @@
         <v>128669862</v>
       </c>
       <c r="B12" t="n">
-        <v>98523</v>
+        <v>98529</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         <v>128669913</v>
       </c>
       <c r="B13" t="n">
-        <v>97556</v>
+        <v>97562</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 27805-2022 artfynd.xlsx
+++ b/artfynd/A 27805-2022 artfynd.xlsx
@@ -1818,7 +1818,7 @@
         <v>128669862</v>
       </c>
       <c r="B12" t="n">
-        <v>98529</v>
+        <v>98536</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         <v>128669913</v>
       </c>
       <c r="B13" t="n">
-        <v>97562</v>
+        <v>97569</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 27805-2022 artfynd.xlsx
+++ b/artfynd/A 27805-2022 artfynd.xlsx
@@ -1818,7 +1818,7 @@
         <v>128669862</v>
       </c>
       <c r="B12" t="n">
-        <v>98536</v>
+        <v>98540</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         <v>128669913</v>
       </c>
       <c r="B13" t="n">
-        <v>97569</v>
+        <v>97573</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 27805-2022 artfynd.xlsx
+++ b/artfynd/A 27805-2022 artfynd.xlsx
@@ -1818,7 +1818,7 @@
         <v>128669862</v>
       </c>
       <c r="B12" t="n">
-        <v>98540</v>
+        <v>98547</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         <v>128669913</v>
       </c>
       <c r="B13" t="n">
-        <v>97573</v>
+        <v>97580</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 27805-2022 artfynd.xlsx
+++ b/artfynd/A 27805-2022 artfynd.xlsx
@@ -1818,7 +1818,7 @@
         <v>128669862</v>
       </c>
       <c r="B12" t="n">
-        <v>98550</v>
+        <v>98555</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         <v>128669913</v>
       </c>
       <c r="B13" t="n">
-        <v>97583</v>
+        <v>97588</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 27805-2022 artfynd.xlsx
+++ b/artfynd/A 27805-2022 artfynd.xlsx
@@ -1818,7 +1818,7 @@
         <v>128669862</v>
       </c>
       <c r="B12" t="n">
-        <v>98555</v>
+        <v>98563</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         <v>128669913</v>
       </c>
       <c r="B13" t="n">
-        <v>97588</v>
+        <v>97596</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 27805-2022 artfynd.xlsx
+++ b/artfynd/A 27805-2022 artfynd.xlsx
@@ -1818,7 +1818,7 @@
         <v>128669862</v>
       </c>
       <c r="B12" t="n">
-        <v>98563</v>
+        <v>98573</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         <v>128669913</v>
       </c>
       <c r="B13" t="n">
-        <v>97596</v>
+        <v>97606</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 27805-2022 artfynd.xlsx
+++ b/artfynd/A 27805-2022 artfynd.xlsx
@@ -1574,7 +1574,7 @@
         <v>127032210</v>
       </c>
       <c r="B10" t="n">
-        <v>41367</v>
+        <v>41361</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 27805-2022 artfynd.xlsx
+++ b/artfynd/A 27805-2022 artfynd.xlsx
@@ -2028,7 +2028,7 @@
         <v>131988004</v>
       </c>
       <c r="B14" t="n">
-        <v>58107</v>
+        <v>58109</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 27805-2022 artfynd.xlsx
+++ b/artfynd/A 27805-2022 artfynd.xlsx
@@ -2028,7 +2028,7 @@
         <v>131988004</v>
       </c>
       <c r="B14" t="n">
-        <v>58109</v>
+        <v>58110</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 27805-2022 artfynd.xlsx
+++ b/artfynd/A 27805-2022 artfynd.xlsx
@@ -2028,7 +2028,7 @@
         <v>131988004</v>
       </c>
       <c r="B14" t="n">
-        <v>58110</v>
+        <v>58114</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 27805-2022 artfynd.xlsx
+++ b/artfynd/A 27805-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>120390961</v>
       </c>
       <c r="B2" t="n">
-        <v>78648</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79408</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -781,62 +776,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121452935</v>
+        <v>107983218</v>
       </c>
       <c r="B3" t="n">
-        <v>57510</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Storvallen B, Jmt</t>
+          <t>Storvallen F, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>356522</v>
+        <v>356826</v>
       </c>
       <c r="R3" t="n">
-        <v>7019013</v>
+        <v>7019261</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -863,12 +844,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-04-09</t>
+          <t>2023-04-09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-04-09</t>
+          <t>2023-04-09</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,6 +863,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -895,51 +882,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121453015</v>
+        <v>121504481</v>
       </c>
       <c r="B4" t="n">
-        <v>57468</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -991,6 +964,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1009,15 +983,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121504481</v>
+        <v>91554785</v>
       </c>
       <c r="B5" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57966</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1025,37 +994,46 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100048</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Storvallen B, Jmt</t>
+          <t>Storvallen F, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>356522</v>
+        <v>356826</v>
       </c>
       <c r="R5" t="n">
-        <v>7019013</v>
+        <v>7019261</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1082,12 +1060,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-04-09</t>
+          <t>2021-03-12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-04-09</t>
+          <t>2021-03-12</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1096,7 +1074,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1115,15 +1092,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121548518</v>
+        <v>121399859</v>
       </c>
       <c r="B6" t="n">
-        <v>57510</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1131,33 +1103,33 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1167,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>356746</v>
+        <v>356826</v>
       </c>
       <c r="R6" t="n">
-        <v>7019244</v>
+        <v>7019261</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1197,12 +1169,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-04-09</t>
+          <t>2024-04-01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-04-09</t>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Trumning hörd från gammelskogen söder om myren.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1229,32 +1206,27 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121548821</v>
+        <v>121548824</v>
       </c>
       <c r="B7" t="n">
-        <v>57468</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1271,7 +1243,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1343,37 +1315,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121548543</v>
+        <v>68162810</v>
       </c>
       <c r="B8" t="n">
-        <v>58001</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57945</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103042</v>
+        <v>100110</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1382,23 +1349,26 @@
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Storvallen F, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>356746</v>
+        <v>356826</v>
       </c>
       <c r="R8" t="n">
-        <v>7019244</v>
+        <v>7019261</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1425,12 +1395,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-04-09</t>
+          <t>2017-10-30</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-04-09</t>
+          <t>2017-10-30</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Uppmärksammades genom att den knackade på min stuga. Födosökte därefter i de gamla fjällbjörkarna.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1457,15 +1442,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121548824</v>
+        <v>79520999</v>
       </c>
       <c r="B9" t="n">
-        <v>57365</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58424</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1473,16 +1453,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>102624</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåhake</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Luscinia svecica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1492,14 +1472,18 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1509,10 +1493,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>356746</v>
+        <v>356826</v>
       </c>
       <c r="R9" t="n">
-        <v>7019244</v>
+        <v>7019261</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1539,12 +1523,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2021-04-15</t>
+          <t>2019-08-21</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2021-04-15</t>
+          <t>2019-08-21</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,10 +1555,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127032210</v>
+        <v>121602998</v>
       </c>
       <c r="B10" t="n">
-        <v>41367</v>
+        <v>58424</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1582,38 +1566,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>215713</v>
+        <v>102624</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grå blåbärsfältmätare</t>
+          <t>Blåhake</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Entephria caesiata</t>
+          <t>Luscinia svecica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>friflygande</t>
+          <t>besöker bebott bo</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1623,10 +1606,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>356746</v>
+        <v>356789</v>
       </c>
       <c r="R10" t="n">
-        <v>7019244</v>
+        <v>7019296</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1653,31 +1636,20 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>16:20</t>
+          <t>2020-06-14</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>16:20</t>
+          <t>2020-06-14</t>
         </is>
       </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF10" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1696,10 +1668,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127742491</v>
+        <v>86094714</v>
       </c>
       <c r="B11" t="n">
-        <v>57845</v>
+        <v>57105</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1707,49 +1679,53 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>102932</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kricka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Anas crecca</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Storvallen skog, Jmt</t>
+          <t>Storvallen F, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>356872</v>
+        <v>356826</v>
       </c>
       <c r="R11" t="n">
-        <v>7019203</v>
+        <v>7019261</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1773,22 +1749,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>16:40</t>
+          <t>2020-06-06</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>16:40</t>
+          <t>2020-06-06</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På myren</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1815,52 +1786,60 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128669862</v>
+        <v>85976370</v>
       </c>
       <c r="B12" t="n">
-        <v>98573</v>
+        <v>57369</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220093</v>
+        <v>102961</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Drillsnäppa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Actitis hypoleucos</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Åre (väg 1018) - Storlien - Norska gränsen, Jmt</t>
+          <t>Storvallen F, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>356859</v>
+        <v>356826</v>
       </c>
       <c r="R12" t="n">
-        <v>7019308</v>
+        <v>7019261</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1884,12 +1863,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2020-06-02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2020-06-02</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1904,26 +1883,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Mika Thunell</t>
+          <t>Ulla Falkdalen</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Noemi Naszarkowski, Anne van Woerkom</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>C250065 AVK krokom och sveg</t>
-        </is>
-      </c>
+          <t>Ulla Falkdalen</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128669913</v>
+        <v>67966377</v>
       </c>
       <c r="B13" t="n">
-        <v>97606</v>
+        <v>58393</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1931,41 +1906,48 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222112</v>
+        <v>102999</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Månlåsbräken</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Botrychium lunaria</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Sw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>sträckande SV</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Åre (väg 1018) - Storlien - Norska gränsen, Jmt</t>
+          <t>Storvallen F, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>357033</v>
+        <v>356826</v>
       </c>
       <c r="R13" t="n">
-        <v>7019072</v>
+        <v>7019261</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1989,12 +1971,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2017-10-15</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2017-10-15</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2009,26 +1991,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Mika Thunell</t>
+          <t>Ulla Falkdalen</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Noemi Naszarkowski, Anne van Woerkom</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>C250065 AVK krokom och sveg</t>
-        </is>
-      </c>
+          <t>Ulla Falkdalen</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131988004</v>
+        <v>85977971</v>
       </c>
       <c r="B14" t="n">
-        <v>58114</v>
+        <v>58388</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2036,21 +2014,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>103001</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2062,7 +2040,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2072,10 +2050,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>356881</v>
+        <v>356826</v>
       </c>
       <c r="R14" t="n">
-        <v>7019227</v>
+        <v>7019261</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2102,22 +2080,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>15:21</t>
+          <t>2020-06-02</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2020-06-02</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2137,10 +2105,2152 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
+          <t>Ulla Falkdalen</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>85976472</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58439</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Storvallen F, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>356826</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7019261</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2020-06-02</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2020-06-02</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Sjunger intill en ny holk.</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Ulla Falkdalen</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Ulla Falkdalen</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>68197438</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Storvallen F, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>356826</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7019261</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2017-11-02</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2017-11-02</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Ulla Falkdalen</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Ulla Falkdalen</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>121452935</v>
+      </c>
+      <c r="B17" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Storvallen B, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>356522</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7019013</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-04-09</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-04-09</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Ulla Falkdalen</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Ulla Falkdalen</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>121548518</v>
+      </c>
+      <c r="B18" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Storvallen F, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>356746</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7019244</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-04-09</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-04-09</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Ulla Falkdalen</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Ulla Falkdalen</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>126011138</v>
+      </c>
+      <c r="B19" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Sundbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>356842</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7019248</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>08:17</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>08:17</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>127742491</v>
+      </c>
+      <c r="B20" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Storvallen skog, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>356872</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7019203</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Ulla Falkdalen</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Ulla Falkdalen</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>131988004</v>
+      </c>
+      <c r="B21" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Storvallen F, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>356881</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7019227</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Ulla Falkdalen</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
           <t>Ulla Falkdalen, Thomas Holmberg</t>
         </is>
       </c>
-      <c r="AY14" t="inlineStr"/>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>68165409</v>
+      </c>
+      <c r="B22" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Storvallen F, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>356826</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7019261</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2017-10-30</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2017-10-30</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Letade föda i en gammal gran utanför stugan.</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Ulla Falkdalen</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Ulla Falkdalen</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>121453015</v>
+      </c>
+      <c r="B23" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Storvallen B, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>356522</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7019013</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-04-09</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-04-09</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Ulla Falkdalen</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Ulla Falkdalen</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>121548517</v>
+      </c>
+      <c r="B24" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Storvallen F, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>356746</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7019244</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-04-09</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-04-09</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Ulla Falkdalen</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Ulla Falkdalen</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>70268422</v>
+      </c>
+      <c r="B25" t="n">
+        <v>58602</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>103042</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Grönfink</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Chloris chloris</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>bobygge</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Storvallen F, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>356826</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7019261</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2018-03-30</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2018-03-30</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Ulla Falkdalen</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Ulla Falkdalen</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>121548543</v>
+      </c>
+      <c r="B26" t="n">
+        <v>58602</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>103042</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Grönfink</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Chloris chloris</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Storvallen F, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>356746</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7019244</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-04-09</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-04-09</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Ulla Falkdalen</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Ulla Falkdalen</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>92387034</v>
+      </c>
+      <c r="B27" t="n">
+        <v>58085</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>205976</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Gråkråka</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Corvus corone cornix</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Storvallen F, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>356826</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7019261</v>
+      </c>
+      <c r="S27" t="n">
+        <v>25</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2021-04-13</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2021-04-13</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Ulla Falkdalen</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Ulla Falkdalen</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>127032210</v>
+      </c>
+      <c r="B28" t="n">
+        <v>41601</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>215713</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Grå blåbärsfältmätare</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Entephria caesiata</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Storvallen F, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>356746</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7019244</v>
+      </c>
+      <c r="S28" t="n">
+        <v>25</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Ulla Falkdalen</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Ulla Falkdalen</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>128669862</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99022</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220093</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Åre (väg 1018) - Storlien - Norska gränsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>356859</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7019308</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Noemi Naszarkowski, Anne van Woerkom</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>C250065 AVK krokom och sveg</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>126011148</v>
+      </c>
+      <c r="B30" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Sundbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>356842</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7019248</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>08:19</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>08:19</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>126011149</v>
+      </c>
+      <c r="B31" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Sundbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>356842</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7019248</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>126437696</v>
+      </c>
+      <c r="B32" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Storvallen F, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>356826</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7019261</v>
+      </c>
+      <c r="S32" t="n">
+        <v>25</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Ulla Falkdalen</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Ulla Falkdalen</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>128669913</v>
+      </c>
+      <c r="B33" t="n">
+        <v>98050</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>222112</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Månlåsbräken</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Botrychium lunaria</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) Sw.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Åre (väg 1018) - Storlien - Norska gränsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>357033</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7019072</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Noemi Naszarkowski, Anne van Woerkom</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>C250065 AVK krokom och sveg</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 27805-2022 artfynd.xlsx
+++ b/artfynd/A 27805-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AY34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1442,27 +1442,27 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>79520999</v>
+        <v>78904391</v>
       </c>
       <c r="B9" t="n">
-        <v>58424</v>
+        <v>57323</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102624</v>
+        <v>100112</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåhake</t>
+          <t>Ljungpipare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Luscinia svecica</t>
+          <t>Pluvialis apricaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1475,15 +1475,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>1K</t>
-        </is>
-      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1523,12 +1519,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2019-08-21</t>
+          <t>2019-07-14</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2019-08-21</t>
+          <t>2019-07-14</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Hörs från myrområde norr om E14 i östra utkanten av Storvallen .</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1555,7 +1566,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121602998</v>
+        <v>79520999</v>
       </c>
       <c r="B10" t="n">
         <v>58424</v>
@@ -1585,18 +1596,18 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>besöker bebott bo</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1606,10 +1617,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>356789</v>
+        <v>356826</v>
       </c>
       <c r="R10" t="n">
-        <v>7019296</v>
+        <v>7019261</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1636,12 +1647,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2020-06-14</t>
+          <t>2019-08-21</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2020-06-14</t>
+          <t>2019-08-21</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1668,10 +1679,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>86094714</v>
+        <v>121602998</v>
       </c>
       <c r="B11" t="n">
-        <v>57105</v>
+        <v>58424</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1679,37 +1690,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102932</v>
+        <v>102624</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kricka</t>
+          <t>Blåhake</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Anas crecca</t>
+          <t>Luscinia svecica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>i par</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>besöker bebott bo</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1719,10 +1730,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>356826</v>
+        <v>356789</v>
       </c>
       <c r="R11" t="n">
-        <v>7019261</v>
+        <v>7019296</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1749,17 +1760,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2020-06-06</t>
+          <t>2020-06-14</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2020-06-06</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På myren</t>
+          <t>2020-06-14</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1786,10 +1792,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>85976370</v>
+        <v>86094714</v>
       </c>
       <c r="B12" t="n">
-        <v>57369</v>
+        <v>57105</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1797,16 +1803,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102961</v>
+        <v>102932</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Drillsnäppa</t>
+          <t>Kricka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Actitis hypoleucos</t>
+          <t>Anas crecca</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1820,10 +1826,14 @@
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1863,12 +1873,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2020-06-02</t>
+          <t>2020-06-06</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2020-06-02</t>
+          <t>2020-06-06</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På myren</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1895,10 +1910,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>67966377</v>
+        <v>85976370</v>
       </c>
       <c r="B13" t="n">
-        <v>58393</v>
+        <v>57369</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1906,16 +1921,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102999</v>
+        <v>102961</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Drillsnäppa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Actitis hypoleucos</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1925,16 +1940,17 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>sträckande SV</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Storvallen F, Jmt</t>
@@ -1971,12 +1987,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2017-10-15</t>
+          <t>2020-06-02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2017-10-15</t>
+          <t>2020-06-02</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2003,10 +2019,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>85977971</v>
+        <v>67966377</v>
       </c>
       <c r="B14" t="n">
-        <v>58388</v>
+        <v>58393</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2014,36 +2030,35 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103001</v>
+        <v>102999</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>70</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
+          <t>sträckande SV</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Storvallen F, Jmt</t>
@@ -2080,12 +2095,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2020-06-02</t>
+          <t>2017-10-15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2020-06-02</t>
+          <t>2017-10-15</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2112,37 +2127,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>85976472</v>
+        <v>85977971</v>
       </c>
       <c r="B15" t="n">
-        <v>58439</v>
+        <v>58388</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103018</v>
+        <v>103001</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -2195,11 +2210,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2020-06-02</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Sjunger intill en ny holk.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2226,46 +2236,47 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>68197438</v>
+        <v>85976472</v>
       </c>
       <c r="B16" t="n">
-        <v>58114</v>
+        <v>58439</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>103018</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Storvallen F, Jmt</t>
@@ -2302,12 +2313,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2017-11-02</t>
+          <t>2020-06-02</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2017-11-02</t>
+          <t>2020-06-02</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Sjunger intill en ny holk.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2334,7 +2350,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121452935</v>
+        <v>68197438</v>
       </c>
       <c r="B17" t="n">
         <v>58114</v>
@@ -2364,27 +2380,26 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Storvallen B, Jmt</t>
+          <t>Storvallen F, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>356522</v>
+        <v>356826</v>
       </c>
       <c r="R17" t="n">
-        <v>7019013</v>
+        <v>7019261</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2411,12 +2426,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-04-09</t>
+          <t>2017-11-02</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-04-09</t>
+          <t>2017-11-02</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2443,7 +2458,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121548518</v>
+        <v>121452935</v>
       </c>
       <c r="B18" t="n">
         <v>58114</v>
@@ -2486,14 +2501,14 @@
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Storvallen F, Jmt</t>
+          <t>Storvallen B, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>356746</v>
+        <v>356522</v>
       </c>
       <c r="R18" t="n">
-        <v>7019244</v>
+        <v>7019013</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2552,7 +2567,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126011138</v>
+        <v>121548518</v>
       </c>
       <c r="B19" t="n">
         <v>58114</v>
@@ -2582,30 +2597,30 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Sundbäcken, Jmt</t>
+          <t>Storvallen F, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>356842</v>
+        <v>356746</v>
       </c>
       <c r="R19" t="n">
-        <v>7019248</v>
+        <v>7019244</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2629,22 +2644,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>08:17</t>
+          <t>2024-04-09</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>08:17</t>
+          <t>2024-04-09</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2659,19 +2664,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Ulla Falkdalen</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Ulla Falkdalen</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127742491</v>
+        <v>126011138</v>
       </c>
       <c r="B20" t="n">
         <v>58114</v>
@@ -2701,30 +2706,30 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Storvallen skog, Jmt</t>
+          <t>Sundbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>356872</v>
+        <v>356842</v>
       </c>
       <c r="R20" t="n">
-        <v>7019203</v>
+        <v>7019248</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2748,22 +2753,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2778,22 +2783,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Ulla Falkdalen</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ulla Falkdalen</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131988004</v>
+        <v>127742491</v>
       </c>
       <c r="B21" t="n">
-        <v>58136</v>
+        <v>58114</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2820,30 +2825,30 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Storvallen F, Jmt</t>
+          <t>Storvallen skog, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>356881</v>
+        <v>356872</v>
       </c>
       <c r="R21" t="n">
-        <v>7019227</v>
+        <v>7019203</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2867,22 +2872,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2902,17 +2907,17 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ulla Falkdalen, Thomas Holmberg</t>
+          <t>Ulla Falkdalen</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>68165409</v>
+        <v>131988004</v>
       </c>
       <c r="B22" t="n">
-        <v>58057</v>
+        <v>58136</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2920,45 +2925,46 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103031</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Storvallen F, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>356826</v>
+        <v>356881</v>
       </c>
       <c r="R22" t="n">
-        <v>7019261</v>
+        <v>7019227</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2985,17 +2991,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2017-10-30</t>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2017-10-30</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Letade föda i en gammal gran utanför stugan.</t>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3015,14 +3026,14 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ulla Falkdalen</t>
+          <t>Ulla Falkdalen, Thomas Holmberg</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121453015</v>
+        <v>68165409</v>
       </c>
       <c r="B23" t="n">
         <v>58057</v>
@@ -3052,27 +3063,26 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Storvallen B, Jmt</t>
+          <t>Storvallen F, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>356522</v>
+        <v>356826</v>
       </c>
       <c r="R23" t="n">
-        <v>7019013</v>
+        <v>7019261</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3099,12 +3109,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-04-09</t>
+          <t>2017-10-30</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-04-09</t>
+          <t>2017-10-30</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Letade föda i en gammal gran utanför stugan.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3131,7 +3146,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121548517</v>
+        <v>121453015</v>
       </c>
       <c r="B24" t="n">
         <v>58057</v>
@@ -3161,7 +3176,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -3174,14 +3189,14 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Storvallen F, Jmt</t>
+          <t>Storvallen B, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>356746</v>
+        <v>356522</v>
       </c>
       <c r="R24" t="n">
-        <v>7019244</v>
+        <v>7019013</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3240,27 +3255,27 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>70268422</v>
+        <v>121548517</v>
       </c>
       <c r="B25" t="n">
-        <v>58602</v>
+        <v>58057</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103042</v>
+        <v>103031</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3273,31 +3288,24 @@
           <t>2</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>bobygge</t>
-        </is>
-      </c>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Storvallen F, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>356826</v>
+        <v>356746</v>
       </c>
       <c r="R25" t="n">
-        <v>7019261</v>
+        <v>7019244</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3324,12 +3332,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2018-03-30</t>
+          <t>2024-04-09</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2018-03-30</t>
+          <t>2024-04-09</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3356,7 +3364,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121548543</v>
+        <v>70268422</v>
       </c>
       <c r="B26" t="n">
         <v>58602</v>
@@ -3386,27 +3394,34 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
+          <t>bobygge</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Storvallen F, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>356746</v>
+        <v>356826</v>
       </c>
       <c r="R26" t="n">
-        <v>7019244</v>
+        <v>7019261</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3433,12 +3448,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-04-09</t>
+          <t>2018-03-30</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-04-09</t>
+          <t>2018-03-30</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3465,44 +3480,44 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>92387034</v>
+        <v>121548543</v>
       </c>
       <c r="B27" t="n">
-        <v>58085</v>
+        <v>58602</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>205976</v>
+        <v>103042</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -3512,10 +3527,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>356826</v>
+        <v>356746</v>
       </c>
       <c r="R27" t="n">
-        <v>7019261</v>
+        <v>7019244</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3542,12 +3557,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2021-04-13</t>
+          <t>2024-04-09</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2021-04-13</t>
+          <t>2024-04-09</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3574,49 +3589,44 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127032210</v>
+        <v>92387034</v>
       </c>
       <c r="B28" t="n">
-        <v>41601</v>
+        <v>58085</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>215713</v>
+        <v>205976</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grå blåbärsfältmätare</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Entephria caesiata</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>friflygande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -3626,10 +3636,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>356746</v>
+        <v>356826</v>
       </c>
       <c r="R28" t="n">
-        <v>7019244</v>
+        <v>7019261</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3656,31 +3666,20 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>16:20</t>
+          <t>2021-04-13</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>16:20</t>
+          <t>2021-04-13</t>
         </is>
       </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF28" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3699,52 +3698,65 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128669862</v>
+        <v>127032210</v>
       </c>
       <c r="B29" t="n">
-        <v>99022</v>
+        <v>41601</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220093</v>
+        <v>215713</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Grå blåbärsfältmätare</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Entephria caesiata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Åre (väg 1018) - Storlien - Norska gränsen, Jmt</t>
+          <t>Storvallen F, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>356859</v>
+        <v>356746</v>
       </c>
       <c r="R29" t="n">
-        <v>7019308</v>
+        <v>7019244</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3768,46 +3780,53 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Mika Thunell</t>
+          <t>Ulla Falkdalen</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Noemi Naszarkowski, Anne van Woerkom</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr">
-        <is>
-          <t>C250065 AVK krokom och sveg</t>
-        </is>
-      </c>
+          <t>Ulla Falkdalen</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126011148</v>
+        <v>128669862</v>
       </c>
       <c r="B30" t="n">
-        <v>97983</v>
+        <v>99022</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3815,41 +3834,41 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221945</v>
+        <v>220093</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Sundbäcken, Jmt</t>
+          <t>Åre (väg 1018) - Storlien - Norska gränsen, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>356842</v>
+        <v>356859</v>
       </c>
       <c r="R30" t="n">
-        <v>7019248</v>
+        <v>7019308</v>
       </c>
       <c r="S30" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3873,22 +3892,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>08:19</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>08:19</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3903,22 +3912,26 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Mika Thunell</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr"/>
+          <t>Noemi Naszarkowski, Anne van Woerkom</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>C250065 AVK krokom och sveg</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126011149</v>
+        <v>126011148</v>
       </c>
       <c r="B31" t="n">
-        <v>99140</v>
+        <v>97983</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3926,30 +3939,26 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
@@ -3993,7 +4002,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4003,7 +4012,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4030,7 +4039,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126437696</v>
+        <v>126011149</v>
       </c>
       <c r="B32" t="n">
         <v>99140</v>
@@ -4058,11 +4067,7 @@
           <t>(L.) Rich.</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
@@ -4073,17 +4078,17 @@
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Storvallen F, Jmt</t>
+          <t>Sundbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>356826</v>
+        <v>356842</v>
       </c>
       <c r="R32" t="n">
-        <v>7019261</v>
+        <v>7019248</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4107,22 +4112,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-07-05</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-07-05</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4137,64 +4142,72 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Ulla Falkdalen</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ulla Falkdalen</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128669913</v>
+        <v>126437696</v>
       </c>
       <c r="B33" t="n">
-        <v>98050</v>
+        <v>99140</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>222112</v>
+        <v>221952</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Månlåsbräken</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Botrychium lunaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Sw.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Åre (väg 1018) - Storlien - Norska gränsen, Jmt</t>
+          <t>Storvallen F, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>357033</v>
+        <v>356826</v>
       </c>
       <c r="R33" t="n">
-        <v>7019072</v>
+        <v>7019261</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4218,12 +4231,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4238,15 +4261,116 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
+          <t>Ulla Falkdalen</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Ulla Falkdalen</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>128669913</v>
+      </c>
+      <c r="B34" t="n">
+        <v>98050</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>222112</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Månlåsbräken</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Botrychium lunaria</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) Sw.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Åre (väg 1018) - Storlien - Norska gränsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>357033</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7019072</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
           <t>Mika Thunell</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
+      <c r="AX34" t="inlineStr">
         <is>
           <t>Noemi Naszarkowski, Anne van Woerkom</t>
         </is>
       </c>
-      <c r="AY33" t="inlineStr">
+      <c r="AY34" t="inlineStr">
         <is>
           <t>C250065 AVK krokom och sveg</t>
         </is>

--- a/artfynd/A 27805-2022 artfynd.xlsx
+++ b/artfynd/A 27805-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY34"/>
+  <dimension ref="A1:AZ34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120390961</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107983218</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -980,6 +995,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121504481</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1089,6 +1109,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91554785</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1203,6 +1228,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121399859</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1312,6 +1342,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121548824</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1439,6 +1474,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68162810</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1563,6 +1603,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78904391</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1676,6 +1721,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79520999</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1789,6 +1839,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121602998</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1907,6 +1962,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86094714</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2016,6 +2076,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85976370</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2124,6 +2189,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67966377</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2233,6 +2303,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85977971</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2347,6 +2422,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85976472</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2455,6 +2535,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68197438</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2564,6 +2649,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121452935</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2673,6 +2763,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121548518</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2792,6 +2887,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126011138</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2911,6 +3011,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127742491</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3030,6 +3135,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131988004</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3143,6 +3253,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68165409</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3252,6 +3367,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121453015</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3361,6 +3481,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121548517</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3477,6 +3602,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70268422</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3586,6 +3716,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121548543</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3695,6 +3830,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92387034</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3820,6 +3960,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127032210</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3923,6 +4068,11 @@
       <c r="AY30" t="inlineStr">
         <is>
           <t>C250065 AVK krokom och sveg</t>
+        </is>
+      </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128669862</t>
         </is>
       </c>
     </row>
@@ -4036,6 +4186,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126011148</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4151,6 +4306,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126011149</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4270,6 +4430,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126437696</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4375,8 +4540,48 @@
           <t>C250065 AVK krokom och sveg</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128669913</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>